--- a/reports/Debug-snowbowl-20251216/For The Day (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251216/For The Day (Prior Year)_Visits.xlsx
@@ -462,7 +462,7 @@
         <v>45643</v>
       </c>
       <c r="C4" s="2">
-        <v>8</v>
+        <v>523</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,10 +476,10 @@
         <v>45643</v>
       </c>
       <c r="C5" s="2">
-        <v>1155</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,10 +490,10 @@
         <v>45643</v>
       </c>
       <c r="C6" s="2">
-        <v>50</v>
+        <v>1155</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,10 +504,10 @@
         <v>45643</v>
       </c>
       <c r="C7" s="2">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,7 +518,7 @@
         <v>45643</v>
       </c>
       <c r="C8" s="2">
-        <v>523</v>
+        <v>71</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
